--- a/حاسب ترم اول.xlsx
+++ b/حاسب ترم اول.xlsx
@@ -442,22 +442,22 @@
         <v>مستجد</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I2">
         <v>20</v>
       </c>
       <c r="J2">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="K2">
-        <v>60</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
@@ -489,10 +489,10 @@
         <v>20</v>
       </c>
       <c r="J3">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="K3">
-        <v>59</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
@@ -512,22 +512,22 @@
         <v>مستجد</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G4" t="str">
         <v>غ</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>20</v>
       </c>
       <c r="J4">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="K4">
-        <v>49</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5">
@@ -547,22 +547,22 @@
         <v>مستجد</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I5">
         <v>6</v>
       </c>
       <c r="J5">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="K5">
-        <v>33</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -582,22 +582,22 @@
         <v>مستجد</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>5</v>
       </c>
       <c r="H6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="K6">
-        <v>69</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
@@ -629,10 +629,10 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="K7">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -664,10 +664,10 @@
         <v>غ</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -699,10 +699,10 @@
         <v>20</v>
       </c>
       <c r="J9">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="K9">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
@@ -734,10 +734,10 @@
         <v>4</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="K10">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -769,10 +769,10 @@
         <v>20</v>
       </c>
       <c r="J11">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="K11">
-        <v>70</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12">
@@ -804,10 +804,10 @@
         <v>8</v>
       </c>
       <c r="J12">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="K12">
-        <v>31</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -839,10 +839,10 @@
         <v>6</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -874,10 +874,10 @@
         <v>20</v>
       </c>
       <c r="J14">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="K14">
-        <v>83</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -909,10 +909,10 @@
         <v>11</v>
       </c>
       <c r="J15">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="K15">
-        <v>66</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -932,22 +932,22 @@
         <v>مستجد</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I16" t="str">
         <v>غ</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K16">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
@@ -967,22 +967,22 @@
         <v>مستجد</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G17">
         <v>2</v>
       </c>
       <c r="H17">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I17">
         <v>9</v>
       </c>
       <c r="J17">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K17">
-        <v>45</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18">
@@ -1002,22 +1002,22 @@
         <v>مستجد</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
       <c r="H18">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I18">
         <v>18</v>
       </c>
       <c r="J18">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K18">
-        <v>40</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -1037,22 +1037,22 @@
         <v>مستجد</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I19">
         <v>8</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K19">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -1084,10 +1084,10 @@
         <v>20</v>
       </c>
       <c r="J20">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K20">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21">
@@ -1107,22 +1107,22 @@
         <v>مستجد</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I21">
         <v>15</v>
       </c>
       <c r="J21">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="K21">
-        <v>65</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22">
@@ -1142,22 +1142,22 @@
         <v>مستجد</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G22">
         <v>4</v>
       </c>
       <c r="H22">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I22">
         <v>16</v>
       </c>
       <c r="J22">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="K22">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23">
@@ -1177,22 +1177,22 @@
         <v>مستجد</v>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>5</v>
       </c>
       <c r="H23">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I23">
         <v>20</v>
       </c>
       <c r="J23">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="K23">
-        <v>55</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24">
@@ -1247,22 +1247,22 @@
         <v>مستجد</v>
       </c>
       <c r="F25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>9</v>
       </c>
       <c r="H25">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I25">
         <v>20</v>
       </c>
       <c r="J25">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K25">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26">
@@ -1282,22 +1282,22 @@
         <v>مستجد</v>
       </c>
       <c r="F26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>3</v>
       </c>
       <c r="H26">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I26">
         <v>10</v>
       </c>
       <c r="J26">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="K26">
-        <v>41</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27">
@@ -1317,22 +1317,22 @@
         <v>مستجد</v>
       </c>
       <c r="F27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>2</v>
       </c>
       <c r="H27">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I27">
         <v>5</v>
       </c>
       <c r="J27">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="K27">
-        <v>43</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28">
@@ -1352,22 +1352,22 @@
         <v>مستجد</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K28">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
@@ -1387,22 +1387,22 @@
         <v>مستجد</v>
       </c>
       <c r="F29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G29">
         <v>2</v>
       </c>
       <c r="H29">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I29">
         <v>18</v>
       </c>
       <c r="J29">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="K29">
-        <v>47</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30">
@@ -1422,22 +1422,22 @@
         <v>مستجد</v>
       </c>
       <c r="F30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I30">
         <v>8</v>
       </c>
       <c r="J30">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="K30">
-        <v>36</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31">
@@ -1469,10 +1469,10 @@
         <v>20</v>
       </c>
       <c r="J31">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="K31">
-        <v>68</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1556,10 +1556,10 @@
         <v>20</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="K2">
-        <v>47</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -1591,10 +1591,10 @@
         <v>20</v>
       </c>
       <c r="J3">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K3">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4">
@@ -1614,22 +1614,22 @@
         <v>مستجد</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G4">
         <v>2</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>8</v>
       </c>
       <c r="J4">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="K4">
-        <v>23</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -1661,10 +1661,10 @@
         <v>20</v>
       </c>
       <c r="J5">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="K5">
-        <v>63</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
@@ -1696,10 +1696,10 @@
         <v>20</v>
       </c>
       <c r="J6">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K6">
-        <v>75</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
@@ -1731,10 +1731,10 @@
         <v>20</v>
       </c>
       <c r="J7">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K7">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8">
@@ -1766,10 +1766,10 @@
         <v>20</v>
       </c>
       <c r="J8">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="K8">
-        <v>69</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
@@ -1801,10 +1801,10 @@
         <v>20</v>
       </c>
       <c r="J9">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="K9">
-        <v>69</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -1836,10 +1836,10 @@
         <v>20</v>
       </c>
       <c r="J10">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="K10">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -1871,10 +1871,10 @@
         <v>20</v>
       </c>
       <c r="J11">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="K11">
-        <v>74</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -1906,10 +1906,10 @@
         <v>20</v>
       </c>
       <c r="J12">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="K12">
-        <v>85</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -1929,22 +1929,22 @@
         <v>مستجد</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I13">
         <v>12</v>
       </c>
       <c r="J13">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K13">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -1976,10 +1976,10 @@
         <v>20</v>
       </c>
       <c r="J14">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="K14">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -1999,22 +1999,22 @@
         <v>مستجد</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>15</v>
       </c>
       <c r="J15">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="K15">
-        <v>26</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2034,22 +2034,22 @@
         <v>مستجد</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="H16">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I16">
         <v>15</v>
       </c>
       <c r="J16">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="K16">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17">
@@ -2081,10 +2081,10 @@
         <v>20</v>
       </c>
       <c r="J17">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="K17">
-        <v>70</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -2116,10 +2116,10 @@
         <v>20</v>
       </c>
       <c r="J18">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K18">
-        <v>77</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19">
@@ -2151,10 +2151,10 @@
         <v>20</v>
       </c>
       <c r="J19">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K19">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20">
@@ -2174,22 +2174,22 @@
         <v>مستجد</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>6</v>
       </c>
       <c r="H20">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I20">
         <v>20</v>
       </c>
       <c r="J20">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="K20">
-        <v>77</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21">
@@ -2209,22 +2209,22 @@
         <v>مستجد</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
       <c r="H21">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I21">
         <v>16</v>
       </c>
       <c r="J21">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="K21">
-        <v>41</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22">
@@ -2256,10 +2256,10 @@
         <v>6</v>
       </c>
       <c r="J22">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="K22">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -2279,22 +2279,22 @@
         <v>مستجد</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>4</v>
       </c>
       <c r="H23">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I23">
         <v>12</v>
       </c>
       <c r="J23">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="K23">
-        <v>46</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24">
@@ -2326,10 +2326,10 @@
         <v>20</v>
       </c>
       <c r="J24">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="K24">
-        <v>85</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25">
@@ -2349,22 +2349,22 @@
         <v>مستجد</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>8</v>
       </c>
       <c r="H25">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I25">
         <v>20</v>
       </c>
       <c r="J25">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="K25">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26">
@@ -2384,22 +2384,22 @@
         <v>مستجد</v>
       </c>
       <c r="F26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>4</v>
       </c>
       <c r="H26">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I26">
         <v>20</v>
       </c>
       <c r="J26">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="K26">
-        <v>67</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27">
@@ -2419,22 +2419,22 @@
         <v>مستجد</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G27">
         <v>4</v>
       </c>
       <c r="H27">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I27">
         <v>18</v>
       </c>
       <c r="J27">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="K27">
-        <v>43</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28">
@@ -2466,10 +2466,10 @@
         <v>20</v>
       </c>
       <c r="J28">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="K28">
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29">
@@ -2489,22 +2489,22 @@
         <v>مستجد</v>
       </c>
       <c r="F29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G29">
         <v>4</v>
       </c>
       <c r="H29">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I29">
         <v>20</v>
       </c>
       <c r="J29">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="K29">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30">
@@ -2536,10 +2536,10 @@
         <v>20</v>
       </c>
       <c r="J30">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K30">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31">
@@ -2559,22 +2559,22 @@
         <v>مستجد</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G31">
         <v>3</v>
       </c>
       <c r="H31">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I31">
         <v>17</v>
       </c>
       <c r="J31">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="K31">
-        <v>58</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2658,10 +2658,10 @@
         <v>20</v>
       </c>
       <c r="J2">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="K2">
-        <v>64</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
@@ -2681,22 +2681,22 @@
         <v>مستجد</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>19</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K3">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
@@ -2716,22 +2716,22 @@
         <v>مستجد</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I4">
         <v>11</v>
       </c>
       <c r="J4">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="K4">
-        <v>30</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
@@ -2751,22 +2751,22 @@
         <v>مستجد</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G5">
         <v>6</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I5">
         <v>17</v>
       </c>
       <c r="J5">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="K5">
-        <v>64</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6">
@@ -2798,10 +2798,10 @@
         <v>20</v>
       </c>
       <c r="J6">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="K6">
-        <v>69</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7">
@@ -2833,10 +2833,10 @@
         <v>20</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K7">
-        <v>64</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8">
@@ -2868,10 +2868,10 @@
         <v>20</v>
       </c>
       <c r="J8">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K8">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9">
@@ -2891,22 +2891,22 @@
         <v>مستجد</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I9">
         <v>11</v>
       </c>
       <c r="J9">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="K9">
-        <v>43</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -2938,10 +2938,10 @@
         <v>20</v>
       </c>
       <c r="J10">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="K10">
-        <v>82</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11">
@@ -2961,22 +2961,22 @@
         <v>مستجد</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>9</v>
       </c>
       <c r="H11">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I11">
         <v>18</v>
       </c>
       <c r="J11">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K11">
-        <v>88</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -2996,22 +2996,22 @@
         <v>مستجد</v>
       </c>
       <c r="F12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>15</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K12">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
@@ -3043,10 +3043,10 @@
         <v>20</v>
       </c>
       <c r="J13">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="K13">
-        <v>84</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -3078,10 +3078,10 @@
         <v>20</v>
       </c>
       <c r="J14">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K14">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -3113,10 +3113,10 @@
         <v>20</v>
       </c>
       <c r="J15">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="K15">
-        <v>69</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
@@ -3148,10 +3148,10 @@
         <v>غ</v>
       </c>
       <c r="J16">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="K16">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -3171,22 +3171,22 @@
         <v>مستجد</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
       <c r="H17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I17">
         <v>20</v>
       </c>
       <c r="J17">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="K17">
-        <v>69</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -3206,22 +3206,22 @@
         <v>مستجد</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
       <c r="H18">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I18">
         <v>8</v>
       </c>
       <c r="J18">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="K18">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -3253,10 +3253,10 @@
         <v>20</v>
       </c>
       <c r="J19">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="K19">
-        <v>84</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20">
@@ -3288,10 +3288,10 @@
         <v>20</v>
       </c>
       <c r="J20">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="K20">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21">
@@ -3311,22 +3311,22 @@
         <v>مستجد</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>5</v>
       </c>
       <c r="H21">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I21">
         <v>15</v>
       </c>
       <c r="J21">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="K21">
-        <v>51</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
@@ -3346,22 +3346,22 @@
         <v>مستجد</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G22">
         <v>6</v>
       </c>
       <c r="H22">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I22">
         <v>15</v>
       </c>
       <c r="J22">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="K22">
-        <v>67</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23">
@@ -3393,10 +3393,10 @@
         <v>20</v>
       </c>
       <c r="J23">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="K23">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24">
@@ -3428,10 +3428,10 @@
         <v>3</v>
       </c>
       <c r="J24">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="K24">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -3451,22 +3451,22 @@
         <v>مستجد</v>
       </c>
       <c r="F25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>7</v>
       </c>
       <c r="H25">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I25">
         <v>20</v>
       </c>
       <c r="J25">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="K25">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26">
@@ -3486,22 +3486,22 @@
         <v>مستجد</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I26">
         <v>9</v>
       </c>
       <c r="J26">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K26">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
@@ -3521,22 +3521,22 @@
         <v>مستجد</v>
       </c>
       <c r="F27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>2</v>
       </c>
       <c r="H27">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I27">
         <v>20</v>
       </c>
       <c r="J27">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="K27">
-        <v>57</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28">
@@ -3568,10 +3568,10 @@
         <v>20</v>
       </c>
       <c r="J28">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="K28">
-        <v>66</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29">
@@ -3603,10 +3603,10 @@
         <v>8</v>
       </c>
       <c r="J29">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K29">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -3638,10 +3638,10 @@
         <v>20</v>
       </c>
       <c r="J30">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="K30">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31">
@@ -3661,22 +3661,22 @@
         <v>مستجد</v>
       </c>
       <c r="F31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>6</v>
       </c>
       <c r="H31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I31">
         <v>20</v>
       </c>
       <c r="J31">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="K31">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -3760,10 +3760,10 @@
         <v>6</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -3783,22 +3783,22 @@
         <v>مستجد</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I3">
         <v>20</v>
       </c>
       <c r="J3">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="K3">
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
@@ -3830,10 +3830,10 @@
         <v>20</v>
       </c>
       <c r="J4">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="K4">
-        <v>83</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5">
@@ -3853,22 +3853,22 @@
         <v>مستجد</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I5">
         <v>8</v>
       </c>
       <c r="J5">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K5">
-        <v>48</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -3900,10 +3900,10 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -3923,22 +3923,22 @@
         <v>مستجد</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>3</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I7">
         <v>17</v>
       </c>
       <c r="J7">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="K7">
-        <v>62</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8">
@@ -3970,10 +3970,10 @@
         <v>20</v>
       </c>
       <c r="J8">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="K8">
-        <v>74</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
@@ -4005,10 +4005,10 @@
         <v>20</v>
       </c>
       <c r="J9">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="K9">
-        <v>74</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -4028,22 +4028,22 @@
         <v>مستجد</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G10">
         <v>2</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I10">
         <v>10</v>
       </c>
       <c r="J10">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="K10">
-        <v>34</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -4063,22 +4063,22 @@
         <v>مستجد</v>
       </c>
       <c r="F11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>6</v>
       </c>
       <c r="H11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I11">
         <v>15</v>
       </c>
       <c r="J11">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K11">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
@@ -4098,22 +4098,22 @@
         <v>مستجد</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>1</v>
       </c>
       <c r="H12">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I12">
         <v>14</v>
       </c>
       <c r="J12">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K12">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -4133,22 +4133,22 @@
         <v>مستجد</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I13">
         <v>20</v>
       </c>
       <c r="J13">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="K13">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -4168,22 +4168,22 @@
         <v>مستجد</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>14</v>
       </c>
       <c r="J14">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="K14">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15">
@@ -4203,22 +4203,22 @@
         <v>مستجد</v>
       </c>
       <c r="F15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>3</v>
       </c>
       <c r="H15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I15">
         <v>20</v>
       </c>
       <c r="J15">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="K15">
-        <v>56</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16">
@@ -4238,22 +4238,22 @@
         <v>مستجد</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>2</v>
       </c>
       <c r="H16">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I16">
         <v>10</v>
       </c>
       <c r="J16">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="K16">
-        <v>27</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -4273,22 +4273,22 @@
         <v>مستجد</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G17">
         <v>2</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I17">
         <v>7</v>
       </c>
       <c r="J17">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="K17">
-        <v>36</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18">
@@ -4320,10 +4320,10 @@
         <v>20</v>
       </c>
       <c r="J18">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K18">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -4355,10 +4355,10 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="K19">
-        <v>36</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20">
@@ -4378,22 +4378,22 @@
         <v>مستجد</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>18</v>
       </c>
       <c r="J20">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="K20">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21">
@@ -4413,22 +4413,22 @@
         <v>مستجد</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>6</v>
       </c>
       <c r="J21">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K21">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
@@ -4448,22 +4448,22 @@
         <v>مستجد</v>
       </c>
       <c r="F22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G22">
         <v>6</v>
       </c>
       <c r="H22">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I22">
         <v>20</v>
       </c>
       <c r="J22">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="K22">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23">
@@ -4483,22 +4483,22 @@
         <v>مستجد</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>2</v>
       </c>
       <c r="H23">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I23">
         <v>15</v>
       </c>
       <c r="J23">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K23">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24">
@@ -4518,22 +4518,22 @@
         <v>مستجد</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I24">
         <v>6</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K24">
-        <v>9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
@@ -4553,22 +4553,22 @@
         <v>مستجد</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G25">
         <v>2</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I25">
         <v>13</v>
       </c>
       <c r="J25">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K25">
-        <v>24</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26">
@@ -4588,22 +4588,22 @@
         <v>مستجد</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I26">
         <v>12</v>
       </c>
       <c r="J26">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K26">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27">
@@ -4623,22 +4623,22 @@
         <v>مستجد</v>
       </c>
       <c r="F27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>6</v>
       </c>
       <c r="J27">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K27">
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28">
@@ -4658,22 +4658,22 @@
         <v>مستجد</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>6</v>
       </c>
       <c r="H28">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I28">
         <v>19</v>
       </c>
       <c r="J28">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="K28">
-        <v>74</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29">
@@ -4693,22 +4693,22 @@
         <v>مستجد</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I29">
         <v>8</v>
       </c>
       <c r="J29">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K29">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30">
@@ -4728,22 +4728,22 @@
         <v>مستجد</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G30">
         <v>4</v>
       </c>
       <c r="H30">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I30">
         <v>15</v>
       </c>
       <c r="J30">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="K30">
-        <v>59</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31">
@@ -4763,22 +4763,22 @@
         <v>مستجد</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I31">
         <v>13</v>
       </c>
       <c r="J31">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K31">
-        <v>23</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -4862,10 +4862,10 @@
         <v>20</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="K2">
-        <v>66</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
@@ -4897,10 +4897,10 @@
         <v>20</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="K3">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
@@ -4920,22 +4920,22 @@
         <v>مستجد</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I4">
         <v>9</v>
       </c>
       <c r="J4">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="K4">
-        <v>40</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -4967,10 +4967,10 @@
         <v>20</v>
       </c>
       <c r="J5">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="K5">
-        <v>81</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6">
@@ -4990,22 +4990,22 @@
         <v>مستجد</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="K6">
-        <v>52</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -5037,10 +5037,10 @@
         <v>20</v>
       </c>
       <c r="J7">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K7">
-        <v>45</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -5072,10 +5072,10 @@
         <v>غ</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -5107,10 +5107,10 @@
         <v>20</v>
       </c>
       <c r="J9">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K9">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10">
@@ -5130,22 +5130,22 @@
         <v>مستجد</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>6</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K10">
-        <v>9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -5177,10 +5177,10 @@
         <v>20</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="K11">
-        <v>66</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12">
@@ -5212,10 +5212,10 @@
         <v>20</v>
       </c>
       <c r="J12">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="K12">
-        <v>79</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -5247,10 +5247,10 @@
         <v>20</v>
       </c>
       <c r="J13">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="K13">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -5270,22 +5270,22 @@
         <v>مستجد</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>7</v>
       </c>
       <c r="H14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I14">
         <v>10</v>
       </c>
       <c r="J14">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="K14">
-        <v>73</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15">
@@ -5317,10 +5317,10 @@
         <v>20</v>
       </c>
       <c r="J15">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="K15">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16">
@@ -5352,10 +5352,10 @@
         <v>19</v>
       </c>
       <c r="J16">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="K16">
-        <v>70</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
@@ -5375,22 +5375,22 @@
         <v>مستجد</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G17">
         <v>2</v>
       </c>
       <c r="H17">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I17">
         <v>7</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K17">
-        <v>16</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -5410,22 +5410,22 @@
         <v>مستجد</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>20</v>
       </c>
       <c r="J18">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K18">
-        <v>41</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5445,22 +5445,22 @@
         <v>مستجد</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>8</v>
       </c>
       <c r="J19">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="K19">
-        <v>33</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20">
@@ -5492,10 +5492,10 @@
         <v>6</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K20">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -5527,10 +5527,10 @@
         <v>20</v>
       </c>
       <c r="J21">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="K21">
-        <v>76</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22">
@@ -5550,22 +5550,22 @@
         <v>مستجد</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G22">
         <v>5</v>
       </c>
       <c r="H22">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I22">
         <v>18</v>
       </c>
       <c r="J22">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="K22">
-        <v>61</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23">
@@ -5585,22 +5585,22 @@
         <v>مستجد</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I23">
         <v>10</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K23">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24">
@@ -5632,10 +5632,10 @@
         <v>20</v>
       </c>
       <c r="J24">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="K24">
-        <v>74</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25">
@@ -5655,22 +5655,22 @@
         <v>مستجد</v>
       </c>
       <c r="F25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>2</v>
       </c>
       <c r="H25">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I25">
         <v>18</v>
       </c>
       <c r="J25">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="K25">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26">
@@ -5737,10 +5737,10 @@
         <v>20</v>
       </c>
       <c r="J27">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K27">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28">
@@ -5772,10 +5772,10 @@
         <v>19</v>
       </c>
       <c r="J28">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="K28">
-        <v>69</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29">
@@ -5795,22 +5795,22 @@
         <v>مستجد</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G29">
         <v>2</v>
       </c>
       <c r="H29">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I29">
         <v>20</v>
       </c>
       <c r="J29">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="K29">
-        <v>56</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30">
@@ -5830,22 +5830,22 @@
         <v>مستجد</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I30">
         <v>15</v>
       </c>
       <c r="J30">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K30">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31">
@@ -5865,22 +5865,22 @@
         <v>مستجد</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I31">
         <v>8</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K31">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -5952,22 +5952,22 @@
         <v>مستجد</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>3</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I2">
         <v>12</v>
       </c>
       <c r="J2">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="K2">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
@@ -5999,10 +5999,10 @@
         <v>20</v>
       </c>
       <c r="J3">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="K3">
-        <v>44</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
@@ -6034,10 +6034,10 @@
         <v>6</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K4">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -6057,22 +6057,22 @@
         <v>مستجد</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>7</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="K5">
-        <v>16</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -6104,10 +6104,10 @@
         <v>غ</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -6127,22 +6127,22 @@
         <v>مستجد</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>20</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K7">
-        <v>26</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -6162,22 +6162,22 @@
         <v>مستجد</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>5</v>
       </c>
       <c r="H8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I8">
         <v>18</v>
       </c>
       <c r="J8">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="K8">
-        <v>76</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9">
@@ -6197,22 +6197,22 @@
         <v>مستجد</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I9">
         <v>16</v>
       </c>
       <c r="J9">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="K9">
-        <v>48</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -6244,10 +6244,10 @@
         <v>20</v>
       </c>
       <c r="J10">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="K10">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
@@ -6267,22 +6267,22 @@
         <v>مستجد</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>18</v>
       </c>
       <c r="J11">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="K11">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12">
@@ -6349,10 +6349,10 @@
         <v>18</v>
       </c>
       <c r="J13">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="K13">
-        <v>66</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14">
@@ -6384,10 +6384,10 @@
         <v>20</v>
       </c>
       <c r="J14">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="K14">
-        <v>83</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -6407,22 +6407,22 @@
         <v>مستجد</v>
       </c>
       <c r="F15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>4</v>
       </c>
       <c r="H15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15">
         <v>16</v>
       </c>
       <c r="J15">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="K15">
-        <v>63</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6442,22 +6442,22 @@
         <v>مستجد</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G16">
         <v>3</v>
       </c>
       <c r="H16">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I16">
         <v>6</v>
       </c>
       <c r="J16">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="K16">
-        <v>36</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17">
@@ -6489,10 +6489,10 @@
         <v>20</v>
       </c>
       <c r="J17">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="K17">
-        <v>82</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18">
@@ -6524,10 +6524,10 @@
         <v>20</v>
       </c>
       <c r="J18">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="K18">
-        <v>77</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19">
@@ -6547,22 +6547,22 @@
         <v>مستجد</v>
       </c>
       <c r="F19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I19">
         <v>13</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K19">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6594,10 +6594,10 @@
         <v>20</v>
       </c>
       <c r="J20">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K20">
-        <v>63</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
@@ -6629,10 +6629,10 @@
         <v>20</v>
       </c>
       <c r="J21">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K21">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22">
@@ -6664,10 +6664,10 @@
         <v>20</v>
       </c>
       <c r="J22">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="K22">
-        <v>83</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23">
@@ -6699,10 +6699,10 @@
         <v>20</v>
       </c>
       <c r="J23">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="K23">
-        <v>68</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24">
@@ -6722,22 +6722,22 @@
         <v>مستجد</v>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>5</v>
       </c>
       <c r="H24">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I24">
         <v>20</v>
       </c>
       <c r="J24">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K24">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25">
@@ -6757,22 +6757,22 @@
         <v>مستجد</v>
       </c>
       <c r="F25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>13</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K25">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
@@ -6792,22 +6792,22 @@
         <v>مستجد</v>
       </c>
       <c r="F26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>5</v>
       </c>
       <c r="H26">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I26">
         <v>16</v>
       </c>
       <c r="J26">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="K26">
-        <v>51</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27">
@@ -6827,22 +6827,22 @@
         <v>مستجد</v>
       </c>
       <c r="F27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>2</v>
       </c>
       <c r="H27">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I27">
         <v>18</v>
       </c>
       <c r="J27">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="K27">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
@@ -6862,22 +6862,22 @@
         <v>مستجد</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>2</v>
       </c>
       <c r="H28">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I28">
         <v>9</v>
       </c>
       <c r="J28">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K28">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
@@ -6897,22 +6897,22 @@
         <v>مستجد</v>
       </c>
       <c r="F29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G29">
         <v>4</v>
       </c>
       <c r="H29">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I29">
         <v>18</v>
       </c>
       <c r="J29">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="K29">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30">
@@ -6932,22 +6932,22 @@
         <v>مستجد</v>
       </c>
       <c r="F30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>7</v>
       </c>
       <c r="H30">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I30">
         <v>20</v>
       </c>
       <c r="J30">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K30">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31">
@@ -6967,22 +6967,22 @@
         <v>مستجد</v>
       </c>
       <c r="F31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>6</v>
       </c>
       <c r="H31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I31">
         <v>20</v>
       </c>
       <c r="J31">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="K31">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -7066,10 +7066,10 @@
         <v>8</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -7089,22 +7089,22 @@
         <v>مستجد</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>5</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I3">
         <v>10</v>
       </c>
       <c r="J3">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K3">
-        <v>50</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
@@ -7136,10 +7136,10 @@
         <v>20</v>
       </c>
       <c r="J4">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="K4">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5">
@@ -7159,22 +7159,22 @@
         <v>مستجد</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I5">
         <v>18</v>
       </c>
       <c r="J5">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="K5">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
@@ -7194,22 +7194,22 @@
         <v>مستجد</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" t="str">
         <v>غ</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>6</v>
       </c>
       <c r="J6">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K6">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -7229,22 +7229,22 @@
         <v>مستجد</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>4</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I7">
         <v>8</v>
       </c>
       <c r="J7">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="K7">
-        <v>39</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -7276,10 +7276,10 @@
         <v>20</v>
       </c>
       <c r="J8">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="K8">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9">
@@ -7311,10 +7311,10 @@
         <v>19</v>
       </c>
       <c r="J9">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="K9">
-        <v>82</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
@@ -7346,10 +7346,10 @@
         <v>20</v>
       </c>
       <c r="J10">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="K10">
-        <v>69</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -7369,22 +7369,22 @@
         <v>مستجد</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>2</v>
       </c>
       <c r="H11">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I11">
         <v>18</v>
       </c>
       <c r="J11">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="K11">
-        <v>58</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
@@ -7416,10 +7416,10 @@
         <v>20</v>
       </c>
       <c r="J12">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="K12">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13">
@@ -7439,22 +7439,22 @@
         <v>مستجد</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>6</v>
       </c>
       <c r="J13">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K13">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -7474,22 +7474,22 @@
         <v>مستجد</v>
       </c>
       <c r="F14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>7</v>
       </c>
       <c r="H14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I14">
         <v>19</v>
       </c>
       <c r="J14">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="K14">
-        <v>73</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15">
@@ -7509,22 +7509,22 @@
         <v>مستجد</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>4</v>
       </c>
       <c r="H15">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I15">
         <v>10</v>
       </c>
       <c r="J15">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="K15">
-        <v>49</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -7579,22 +7579,22 @@
         <v>مستجد</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>3</v>
       </c>
       <c r="H17">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I17">
         <v>20</v>
       </c>
       <c r="J17">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="K17">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -7614,22 +7614,22 @@
         <v>مستجد</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>17</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K18">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -7661,10 +7661,10 @@
         <v>20</v>
       </c>
       <c r="J19">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K19">
-        <v>77</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20">
@@ -7684,22 +7684,22 @@
         <v>مستجد</v>
       </c>
       <c r="F20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>3</v>
       </c>
       <c r="H20">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I20">
         <v>20</v>
       </c>
       <c r="J20">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="K20">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21">
@@ -7719,22 +7719,22 @@
         <v>مستجد</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I21">
         <v>20</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K21">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -7766,10 +7766,10 @@
         <v>20</v>
       </c>
       <c r="J22">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K22">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23">
@@ -7789,22 +7789,22 @@
         <v>باقي</v>
       </c>
       <c r="F23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>2</v>
       </c>
       <c r="H23">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I23">
         <v>14</v>
       </c>
       <c r="J23">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K23">
-        <v>37</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24">
@@ -7836,10 +7836,10 @@
         <v>18</v>
       </c>
       <c r="J24">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="K24">
-        <v>38</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25">
@@ -7906,10 +7906,10 @@
         <v>20</v>
       </c>
       <c r="J26">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K26">
-        <v>45</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27">
@@ -7976,10 +7976,10 @@
         <v>6</v>
       </c>
       <c r="J28">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K28">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
@@ -8011,10 +8011,10 @@
         <v>11</v>
       </c>
       <c r="J29">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="K29">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30">
@@ -8034,22 +8034,22 @@
         <v>باقي</v>
       </c>
       <c r="F30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>5</v>
       </c>
       <c r="H30">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I30">
         <v>15</v>
       </c>
       <c r="J30">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K30">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31">
@@ -8168,10 +8168,10 @@
         <v>غ</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -8191,22 +8191,22 @@
         <v>باقي</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>8</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K3">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -8238,10 +8238,10 @@
         <v>6</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -8273,10 +8273,10 @@
         <v>20</v>
       </c>
       <c r="J5">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="K5">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -8308,10 +8308,10 @@
         <v>غ</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -8343,10 +8343,10 @@
         <v>غ</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -8378,10 +8378,10 @@
         <v>غ</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -8448,10 +8448,10 @@
         <v>غ</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -8471,22 +8471,22 @@
         <v>باقي</v>
       </c>
       <c r="F11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>2</v>
       </c>
       <c r="H11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I11">
         <v>18</v>
       </c>
       <c r="J11">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="K11">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12">
@@ -8518,10 +8518,10 @@
         <v>غ</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -8553,10 +8553,10 @@
         <v>8</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K13">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
@@ -8575,8 +8575,8 @@
       <c r="E14" t="str">
         <v>باقي</v>
       </c>
-      <c r="F14">
-        <v>0</v>
+      <c r="F14" t="str">
+        <v>غ</v>
       </c>
       <c r="G14" t="str">
         <v>غ</v>
@@ -8658,10 +8658,10 @@
         <v>6</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -8728,10 +8728,10 @@
         <v>غ</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K18">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -8821,22 +8821,22 @@
         <v>باقي</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G21">
         <v>4</v>
       </c>
       <c r="H21">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I21">
         <v>17</v>
       </c>
       <c r="J21">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="K21">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22">
@@ -8868,10 +8868,10 @@
         <v>9</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K22">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -8891,22 +8891,22 @@
         <v>مستجد</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I23">
         <v>16</v>
       </c>
       <c r="J23">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="K23">
-        <v>50</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
@@ -8926,22 +8926,22 @@
         <v>مستجد</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>3</v>
       </c>
       <c r="H24">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I24">
         <v>20</v>
       </c>
       <c r="J24">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="K24">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
@@ -8973,10 +8973,10 @@
         <v>20</v>
       </c>
       <c r="J25">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="K25">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
